--- a/output/2026-10-02_17_Malesia_Pahang_Cleaning.xlsx
+++ b/output/2026-10-02_17_Malesia_Pahang_Cleaning.xlsx
@@ -494,7 +494,6 @@
           <t>09 567 1688</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Sede fisica confermata a Kuantan, Pahang (Lot 114 &amp; 115A, Jalan Industri Semambu 7, Kawasan Perindustrian Semambu). Fornitore ibrido: eroga servizi di pulizia/facility management (Nurakleen) e fornisce/noleggia prodotti chimici industriali e attrezzature (Nurachem) ad aziende industriali; verificare umanamente se vende anche a rivenditori terzi o solo direttamente come servizio/fornitura diretta ai clienti industriali.</t>
@@ -502,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -544,7 +543,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -569,8 +568,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Distributore storico dal 1971, leader indipendente nel Sud-Est asiatico di macchine/utensili/chimici per pulizia industriale e municipale. Sede a Shah Alam, Selangor (non in Pahang); copertura locale in Pahang non confermata; numero HQ Singapore non attribuibile con certezza all'entità malese, lasciato vuoto.</t>
@@ -578,7 +575,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -608,7 +605,6 @@
           <t>+60 3 8070 2826</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Fornitore di attrezzature/veicoli per pulizia industriale, stradale e aeroportuale dal 1996. Dealer di Bucher Municipal (sweeper), Hako-Werke, PowerBoss Minuteman, DISAB-TELLA, Beam A/S, Sides. Sede a Puchong, Selangor (non in Pahang); copertura locale in Pahang non confermata.</t>
@@ -616,7 +612,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -626,7 +622,6 @@
           <t>Floormac (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Pahang</t>
@@ -637,8 +632,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Importatore/distributore di attrezzature per pulizia pavimenti e heavy-duty, prodotti chimici; dealer autorizzato Nilfisk, RCM SPA, FASA, 3M, REN. Sede a Subang Jaya, Selangor (non in Pahang); SSM n. 201801018274; sito web non confermato con certezza; copertura locale in Pahang non confermata.</t>
@@ -646,7 +639,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -676,7 +669,6 @@
           <t>1-300-22-3188</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Filiale ufficiale Malaysia del gruppo Kärcher: pulitrici alta pressione e cura pavimenti con rete dealer B2B. Sede a Shah Alam, Selangor; Kärcher Centre anche a Penang e Johor Bahru (nessuno in Pahang); presenza fisica/copertura locale in Pahang non confermata.</t>
@@ -684,7 +676,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -714,7 +706,6 @@
           <t>+603 6420 8200</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Divisione Industrial Equipment di Sime UMW, distributore ufficiale Tennant (spazzatrici, lavasciuga industriali); copertura dichiarata Malaysia/Brunei/Singapore/Vietnam/Cina. Sede non in Pahang; copertura locale in Pahang non confermata.</t>
@@ -722,7 +713,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
